--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561556251</v>
+        <v>46157.93069515865</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93069515865</v>
+        <v>46157.93152078529</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93152078529</v>
+        <v>46157.93393263897</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393263897</v>
+        <v>46157.93707518119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93707518119</v>
+        <v>46158.2821029248</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821029248</v>
+        <v>46158.29665210137</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665210137</v>
+        <v>46158.29804267572</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804267572</v>
+        <v>46158.33380990986</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33380990986</v>
+        <v>46158.36847352207</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847352207</v>
+        <v>46158.37281229323</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
